--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K226"/>
+  <dimension ref="A1:K227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5353,12 +5353,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>trabajo_2001_2023</t>
+          <t>por_tipo_1998_2025</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Tabulados Básicos</t>
+          <t>Por Tipo</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5368,27 +5368,27 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/TRABAJO-2001-2023.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/POR-TIPO-1998-2025.xlsx</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>NACIONAL</t>
+          <t>NBI</t>
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>776</v>
+        <v>32</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>29868</v>
+        <v>322</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>por_tipo_1998_2023</t>
+          <t>por_variable_1998_2025</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Por Tipo</t>
+          <t>Por Variable</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-TIPO-1998-2023.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/POR-VARIABLE-1998-2025.xlsx</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
@@ -5447,42 +5447,42 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>por_variable_1998_2023</t>
+          <t>divorcios</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Por Variable</t>
+          <t>Divorcios</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Encuesta de hogares</t>
+          <t>Estadísticas vitales</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-VARIABLE-1998-2023.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/DIVORCIOS.xls</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>NBI</t>
+          <t>DIVORCIOS</t>
         </is>
       </c>
       <c r="G110" s="5" t="n">
         <v>30</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>165</v>
+        <v>602</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
@@ -5494,12 +5494,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>divorcios</t>
+          <t>por_entidad_defunciones</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Divorcios</t>
+          <t>Por Entidad</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/DIVORCIOS.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Defunciones.xls</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>DIVORCIOS</t>
+          <t>DEFUNCIONES</t>
         </is>
       </c>
       <c r="G111" s="5" t="n">
@@ -5529,7 +5529,7 @@
         <v>24</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>602</v>
+        <v>630</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>por_entidad_defunciones</t>
+          <t>por_entidad_matrimonios</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -5561,22 +5561,22 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Defunciones.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Matrimonios.xls</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>DEFUNCIONES</t>
+          <t>MATRIMONIOS</t>
         </is>
       </c>
       <c r="G112" s="5" t="n">
         <v>30</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>630</v>
+        <v>602</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>por_entidad_matrimonios</t>
+          <t>por_entidad_nacimientos</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -5608,22 +5608,22 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Matrimonios.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-nacimientos.xls</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>MATRIMONIOS</t>
+          <t>NACIMIENTOS</t>
         </is>
       </c>
       <c r="G113" s="5" t="n">
         <v>30</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>602</v>
+        <v>628</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
@@ -5635,12 +5635,12 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>por_entidad_nacimientos</t>
+          <t>por_municipios_defunciones</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Por Entidad</t>
+          <t>Por Municipios</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -5655,22 +5655,22 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-nacimientos.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-DEFUNCIONES.xls</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>NACIMIENTOS</t>
+          <t>DEFUNCIONES</t>
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>30</v>
+        <v>409</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>628</v>
+        <v>2388</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>por_municipios_defunciones</t>
+          <t>por_municipios_matrimonios</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-DEFUNCIONES.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-Matrimonios.xls</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>DEFUNCIONES</t>
+          <t>MATRIMONIOS</t>
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>7</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>2388</v>
+        <v>2178</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>por_municipios_matrimonios</t>
+          <t>por_municipios_nacimientos</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -5749,22 +5749,22 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-Matrimonios.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-nacimientos.xls</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>MATRIMONIOS</t>
+          <t>NACIMIENTOS</t>
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="H116" s="5" t="n">
         <v>7</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>2178</v>
+        <v>2377</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
@@ -5776,12 +5776,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>por_municipios_nacimientos</t>
+          <t>suicidios</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Por Municipios</t>
+          <t>Suicidios</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -5796,22 +5796,22 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-nacimientos.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/SUICIDIOS.xls</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>NACIMIENTOS</t>
+          <t>SUICIDIOS</t>
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>407</v>
+        <v>30</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>2377</v>
+        <v>603</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -5823,17 +5823,17 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>suicidios</t>
+          <t>amazonas</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Suicidios</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas vitales</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -5843,22 +5843,22 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/SUICIDIOS.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Amazonas.xls</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>SUICIDIOS</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>30</v>
+        <v>666</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>603</v>
+        <v>50624</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>amazonas</t>
+          <t>estado_amazonas_1</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -5890,22 +5890,22 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Amazonas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-1.xls</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Amazonas</t>
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>666</v>
+        <v>36</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>50624</v>
+        <v>1303</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>estado_amazonas_1</t>
+          <t>estado_amazonas</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas.xls</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -5946,13 +5946,13 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>1303</v>
+        <v>807</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>estado_amazonas</t>
+          <t>estado_amazonas_3</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Amazonas-3.xls</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -5993,13 +5993,13 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>807</v>
+        <v>1303</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
@@ -6011,12 +6011,12 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>estado_amazonas_3</t>
+          <t>anzoategui</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -6031,22 +6031,22 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Amazonas-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Anzoategui.xls</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Estado Amazonas</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>36</v>
+        <v>1384</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>1303</v>
+        <v>105211</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>anzoategui</t>
+          <t>estado_anzoategui_1</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -6078,22 +6078,22 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Anzoategui.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-1.xls</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Anzoátegui</t>
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1384</v>
+        <v>78</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>105211</v>
+        <v>3487</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>estado_anzoategui_1</t>
+          <t>estado_anzoategui</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui.xls</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -6137,10 +6137,10 @@
         <v>78</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>3487</v>
+        <v>807</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>estado_anzoategui</t>
+          <t>estado_anzoategui_3</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Anzoategui-3.xls</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -6184,10 +6184,10 @@
         <v>78</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>807</v>
+        <v>3487</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -6199,12 +6199,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>estado_anzoategui_3</t>
+          <t>apure</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -6219,22 +6219,22 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Anzoategui-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Apure.xls</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Estado Anzoátegui</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>78</v>
+        <v>1392</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>3487</v>
+        <v>105839</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>apure</t>
+          <t>estado_apure_1</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -6266,22 +6266,22 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Apure.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-1.xls</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Apure</t>
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>1392</v>
+        <v>36</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>105839</v>
+        <v>1303</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>estado_apure_1</t>
+          <t>estado_apure</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure.xls</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -6322,13 +6322,13 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H128" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>1303</v>
+        <v>807</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>estado_apure</t>
+          <t>estado_apure_3</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Apure-3.xls</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -6369,13 +6369,13 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>807</v>
+        <v>1303</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
@@ -6387,12 +6387,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>estado_apure_3</t>
+          <t>barinas</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Apure-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Barinas.xls</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Estado Apure</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>36</v>
+        <v>2011</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>1303</v>
+        <v>152836</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>barinas</t>
+          <t>estado_barinas_1</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -6454,22 +6454,22 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Barinas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas-1.xls</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Barinas</t>
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>2011</v>
+        <v>51</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>152836</v>
+        <v>2083</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>estado_barinas_1</t>
+          <t>estado_barinas</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas.xls</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -6510,13 +6510,13 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>2083</v>
+        <v>807</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>estado_barinas</t>
+          <t>estado_barinas_3</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Barinas-3.xls</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -6557,13 +6557,13 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>807</v>
+        <v>2083</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
@@ -6575,12 +6575,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>estado_barinas_3</t>
+          <t>bolivar</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Barinas-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Bolivar.xls</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Estado Barinas</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>51</v>
+        <v>1810</v>
       </c>
       <c r="H134" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>2083</v>
+        <v>137582</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>bolivar</t>
+          <t>estado_bolivar_1</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -6642,22 +6642,22 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Bolivar.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-1.xls</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Bolívar</t>
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>1810</v>
+        <v>48</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>137582</v>
+        <v>1927</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>estado_bolivar_1</t>
+          <t>estado_bolivar</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar.xls</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -6698,13 +6698,13 @@
         </is>
       </c>
       <c r="G136" s="5" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="H136" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>1927</v>
+        <v>807</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>estado_bolivar</t>
+          <t>estado_bolivar_4</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Bolivar-4.xls</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>807</v>
+        <v>1927</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -6763,12 +6763,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>estado_bolivar_4</t>
+          <t>carabobo</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -6783,22 +6783,22 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Bolivar-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Carabobo.xls</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Estado Bolívar</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G138" s="5" t="n">
-        <v>48</v>
+        <v>388</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>1927</v>
+        <v>29489</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>carabobo</t>
+          <t>estado_carabobo_1</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -6830,22 +6830,22 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Carabobo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-1.xls</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Carabobo</t>
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>388</v>
+        <v>57</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>29489</v>
+        <v>2395</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>estado_carabobo_1</t>
+          <t>estado_carabobo</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo.xls</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -6886,13 +6886,13 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="H140" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>2395</v>
+        <v>807</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>estado_carabobo</t>
+          <t>estado_carabobo_4</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Carabobo-4.xls</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>807</v>
+        <v>2395</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -6951,12 +6951,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>estado_carabobo_4</t>
+          <t>cojedes</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -6971,22 +6971,22 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Carabobo-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Cojedes.xls</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Estado Carabobo</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>57</v>
+        <v>537</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>2395</v>
+        <v>40813</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>cojedes</t>
+          <t>estado_cojedes_1</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -7018,22 +7018,22 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Cojedes.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-1.xls</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Cojedes</t>
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>537</v>
+        <v>42</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>40813</v>
+        <v>1615</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>estado_cojedes_1</t>
+          <t>estado_cojedes</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes.xls</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -7074,13 +7074,13 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>1615</v>
+        <v>807</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>estado_cojedes</t>
+          <t>estado_cojedes_5</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Cojedes-5.xls</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -7121,13 +7121,13 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>807</v>
+        <v>1615</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
@@ -7139,12 +7139,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>estado_cojedes_5</t>
+          <t>delta_amacuro</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -7159,22 +7159,22 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Cojedes-5.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Estado Cojedes</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>42</v>
+        <v>587</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>1615</v>
+        <v>44626</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>delta_amacuro</t>
+          <t>estado_delta_amacuro_1</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -7206,22 +7206,22 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Delta-Amacuro.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-1.xls</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Delta Amacuro</t>
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>587</v>
+        <v>27</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>44626</v>
+        <v>835</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>estado_delta_amacuro_1</t>
+          <t>estado_delta_amacuro</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -7262,13 +7262,13 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>835</v>
+        <v>807</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>estado_delta_amacuro</t>
+          <t>estado_deltaamacuro_4</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_DeltaAmacuro-4.xls</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -7309,13 +7309,13 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>807</v>
+        <v>835</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -7327,12 +7327,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>estado_deltaamacuro_4</t>
+          <t>dependencias_federales_1</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Dep. Federales</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -7347,22 +7347,22 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_DeltaAmacuro-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-1.xls</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Estado Delta Amacuro</t>
+          <t>Dependencias Federales</t>
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H150" s="5" t="n">
         <v>53</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>835</v>
+        <v>211</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>dependencias_federales_1</t>
+          <t>dependencias_federales</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales.xls</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>211</v>
+        <v>807</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
@@ -7421,12 +7421,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>dependencias_federales</t>
+          <t>dependencias_federales_3</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Dep. Federales</t>
+          <t>Dependencias Federales</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias_Federales-3.xls</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -7450,13 +7450,13 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>807</v>
+        <v>211</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -7468,12 +7468,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>dependencias_federales_3</t>
+          <t>distrito_capital_1</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Dependencias Federales</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -7488,22 +7488,22 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias_Federales-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-1.xls</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Dependencias Federales</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="H153" s="5" t="n">
         <v>53</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>211</v>
+        <v>3643</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>distrito_capital_1</t>
+          <t>distrito_capital_2</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -7535,22 +7535,22 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-2.xls</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>3643</v>
+        <v>2205</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>distrito_capital_2</t>
+          <t>distrito_capital</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -7582,22 +7582,22 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-2.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital.xls</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>2205</v>
+        <v>807</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>distrito_capital</t>
+          <t>distrito_capital_3</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito_Capital-3.xls</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
@@ -7638,13 +7638,13 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H156" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>807</v>
+        <v>3643</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
@@ -7656,12 +7656,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>distrito_capital_3</t>
+          <t>estado_falcon_1</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -7676,22 +7676,22 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito_Capital-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-1.xls</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Estado Falcón</t>
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H157" s="5" t="n">
         <v>53</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>3643</v>
+        <v>4111</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>estado_falcon_1</t>
+          <t>estado_falcon</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon.xls</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>4111</v>
+        <v>807</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>estado_falcon</t>
+          <t>estado_falcon_4</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Falcon-4.xls</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -7779,13 +7779,13 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>807</v>
+        <v>4111</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>estado_falcon_4</t>
+          <t>falcon</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -7817,22 +7817,22 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Falcon-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Falcon.xls</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>Estado Falcón</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>90</v>
+        <v>2086</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>4111</v>
+        <v>158537</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
@@ -7844,12 +7844,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>falcon</t>
+          <t>estado_guarico_1</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -7864,22 +7864,22 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Falcon.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-1.xls</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Guárico</t>
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>2086</v>
+        <v>60</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>158537</v>
+        <v>2551</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>estado_guarico_1</t>
+          <t>estado_guarico</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico.xls</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -7920,13 +7920,13 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H162" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>2551</v>
+        <v>807</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>estado_guarico</t>
+          <t>estado_guarico_4</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Guarico-4.xls</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -7967,13 +7967,13 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>807</v>
+        <v>2551</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>estado_guarico_4</t>
+          <t>guarico</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -8005,22 +8005,22 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Guarico-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Guarico.xls</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>Estado Guárico</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>60</v>
+        <v>2450</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>2551</v>
+        <v>186201</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
@@ -8032,12 +8032,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>guarico</t>
+          <t>estado_la_guaira_1</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -8052,22 +8052,22 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Guarico.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-1.xls</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Vargas</t>
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>2450</v>
+        <v>48</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>186201</v>
+        <v>1927</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>estado_la_guaira_1</t>
+          <t>estado_la_guaira</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira.xls</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -8108,13 +8108,13 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="H166" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>1927</v>
+        <v>807</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>estado_la_guaira</t>
+          <t>estado_vargas_4</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Vargas-4.xls</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -8155,13 +8155,13 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="H167" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>807</v>
+        <v>1927</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>estado_vargas_4</t>
+          <t>vargas</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -8193,22 +8193,22 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Vargas-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Vargas.xls</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>Estado Vargas</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="H168" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>1927</v>
+        <v>12465</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
@@ -8220,12 +8220,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>vargas</t>
+          <t>estado_lara_1</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -8240,22 +8240,22 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Vargas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-1.xls</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="H169" s="5" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>12465</v>
+        <v>4159</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>Indice de Masculinidad ENT</t>
+          <t>Estado Lara</t>
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="H170" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>4159</v>
+        <v>1615</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>estado_lara_1</t>
+          <t>estado_lara</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara.xls</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -8343,13 +8343,13 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>1615</v>
+        <v>807</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>estado_lara</t>
+          <t>estado_lara_3</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -8381,22 +8381,22 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Lara-3.xls</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>Estado Lara</t>
+          <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H172" s="5" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>807</v>
+        <v>4159</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
@@ -8433,17 +8433,17 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Indice de Masculinidad ENT</t>
+          <t>Estado Lara</t>
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="H173" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>4159</v>
+        <v>1615</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>estado_lara_3</t>
+          <t>lara</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -8475,22 +8475,22 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Lara-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lara.xls</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>Estado Lara</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>42</v>
+        <v>2231</v>
       </c>
       <c r="H174" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>1615</v>
+        <v>169557</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
@@ -8502,12 +8502,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>lara</t>
+          <t>estado_miranda_1</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -8522,22 +8522,22 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lara.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-1.xls</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Miranda</t>
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>2231</v>
+        <v>78</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>169557</v>
+        <v>3487</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>estado_miranda_1</t>
+          <t>estado_miranda</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda.xls</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -8581,10 +8581,10 @@
         <v>78</v>
       </c>
       <c r="H176" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>3487</v>
+        <v>807</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>estado_miranda</t>
+          <t>estado_miranda_5</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Miranda-5.xls</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -8628,10 +8628,10 @@
         <v>78</v>
       </c>
       <c r="H177" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>807</v>
+        <v>3487</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>estado_miranda_5</t>
+          <t>miranda</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -8663,22 +8663,22 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Miranda-5.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Miranda.xls</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>Estado Miranda</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>78</v>
+        <v>699</v>
       </c>
       <c r="H178" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>3487</v>
+        <v>53125</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
@@ -8690,12 +8690,12 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>miranda</t>
+          <t>estado_monagas_1</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -8710,22 +8710,22 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Miranda.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-1.xls</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Monagas</t>
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>699</v>
+        <v>54</v>
       </c>
       <c r="H179" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>53125</v>
+        <v>2239</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>estado_monagas_1</t>
+          <t>estado_monagas</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas.xls</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -8766,13 +8766,13 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="H180" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>2239</v>
+        <v>807</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>estado_monagas</t>
+          <t>estado_monagas_4</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Monagas-4.xls</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -8813,13 +8813,13 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="H181" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>807</v>
+        <v>2239</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>estado_monagas_4</t>
+          <t>monagas</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -8851,22 +8851,22 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Monagas-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Monagas.xls</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>Estado Monagas</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>54</v>
+        <v>796</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>2239</v>
+        <v>60507</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
@@ -8878,12 +8878,12 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>monagas</t>
+          <t>estado_merida_1</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -8898,22 +8898,22 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Monagas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-1.xls</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Mérida</t>
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>796</v>
+        <v>84</v>
       </c>
       <c r="H183" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>60507</v>
+        <v>3799</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>estado_merida_1</t>
+          <t>estado_merida</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida.xls</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -8954,13 +8954,13 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H184" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>3799</v>
+        <v>807</v>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>estado_merida</t>
+          <t>estado_merida_4</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Merida-4.xls</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>807</v>
+        <v>3799</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>estado_merida_4</t>
+          <t>merida</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -9039,22 +9039,22 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Merida-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Merida.xls</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>Estado Mérida</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>84</v>
+        <v>1649</v>
       </c>
       <c r="H186" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>3799</v>
+        <v>125325</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
@@ -9066,12 +9066,12 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>merida</t>
+          <t>nacional_1</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -9086,22 +9086,22 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Merida.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-1.xls</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Resumen Entidad</t>
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>1649</v>
+        <v>93</v>
       </c>
       <c r="H187" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>125325</v>
+        <v>4113</v>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>nacional_1</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -9133,22 +9133,22 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional.xls</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>Resumen Entidad</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H188" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>4113</v>
+        <v>807</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
@@ -9160,12 +9160,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>estado_nueva_esparta_1</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta-1.xls</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H189" s="5" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>807</v>
+        <v>4159</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
@@ -9232,17 +9232,17 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>Indice de Masculinidad ENT</t>
+          <t>Estado Nueva Esparta</t>
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="H190" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>4159</v>
+        <v>1927</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>estado_nueva_esparta_1</t>
+          <t>estado_nueva_esparta</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="H191" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>1927</v>
+        <v>807</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>estado_nueva_esparta</t>
+          <t>estado_nuevaesparta_4</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -9321,22 +9321,22 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_NuevaEsparta-4.xls</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>Estado Nueva Esparta</t>
+          <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H192" s="5" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>807</v>
+        <v>4159</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
@@ -9373,17 +9373,17 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Indice de Masculinidad ENT</t>
+          <t>Estado Nueva Esparta</t>
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="H193" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>4159</v>
+        <v>1927</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>estado_nuevaesparta_4</t>
+          <t>nueva_esparta</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -9415,22 +9415,22 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_NuevaEsparta-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>Estado Nueva Esparta</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="H194" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>1927</v>
+        <v>5245</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
@@ -9442,12 +9442,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>nueva_esparta</t>
+          <t>estado_portuguesa_1</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -9462,22 +9462,22 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nueva-Esparta.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa-1.xls</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Portuguesa</t>
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H195" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>5245</v>
+        <v>2395</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>estado_portuguesa_1</t>
+          <t>estado_portuguesa</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa.xls</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="H196" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>2395</v>
+        <v>807</v>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>estado_portuguesa</t>
+          <t>estado_portuguesa_4</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Portuguesa-4.xls</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -9565,13 +9565,13 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="H197" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>807</v>
+        <v>2395</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>estado_portuguesa_4</t>
+          <t>portuguesa</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -9603,22 +9603,22 @@
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Portuguesa-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Portuguesa.xls</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>Estado Portuguesa</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>57</v>
+        <v>1600</v>
       </c>
       <c r="H198" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>2395</v>
+        <v>121601</v>
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
@@ -9630,12 +9630,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>portuguesa</t>
+          <t>estado_sucre_1</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -9650,22 +9650,22 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Portuguesa.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-1.xls</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Sucre</t>
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>1600</v>
+        <v>60</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>121601</v>
+        <v>2551</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>estado_sucre_1</t>
+          <t>estado_sucre</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre.xls</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -9706,13 +9706,13 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H200" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>2551</v>
+        <v>807</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>estado_sucre</t>
+          <t>estado_sucre_6</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Sucre-6.xls</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -9753,13 +9753,13 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H201" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>807</v>
+        <v>2551</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>estado_sucre_6</t>
+          <t>sucre</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -9791,22 +9791,22 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Sucre-6.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Sucre.xls</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>Estado Sucre</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>60</v>
+        <v>874</v>
       </c>
       <c r="H202" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>2551</v>
+        <v>66431</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
@@ -9818,12 +9818,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>sucre</t>
+          <t>estado_tachira</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Tachira</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Sucre.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira.xls</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Táchira</t>
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>874</v>
+        <v>78</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>66431</v>
+        <v>807</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -9865,12 +9865,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>estado_tachira</t>
+          <t>estado_trujillo_1</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Tachira</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -9885,22 +9885,22 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-1.xls</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Estado Táchira</t>
+          <t>Estado Trujillo</t>
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H204" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>807</v>
+        <v>3331</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>estado_trujillo_1</t>
+          <t>estado_trujillo</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo.xls</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H205" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>3331</v>
+        <v>807</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>estado_trujillo</t>
+          <t>estado_trujillo_3</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Trujillo-3.xls</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -9988,13 +9988,13 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H206" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>807</v>
+        <v>3331</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>estado_trujillo_3</t>
+          <t>trujillo</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -10026,22 +10026,22 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Trujillo-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Trujillo.xls</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Estado Trujillo</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>75</v>
+        <v>1527</v>
       </c>
       <c r="H207" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>3331</v>
+        <v>116054</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
@@ -10053,12 +10053,12 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>trujillo</t>
+          <t>estado_tachira_1</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -10073,22 +10073,22 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Trujillo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-1.xls</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Táchira</t>
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1527</v>
+        <v>102</v>
       </c>
       <c r="H208" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>116054</v>
+        <v>4735</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>estado_tachira_1</t>
+          <t>estado_tachira_8</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Tachira-8.xls</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -10147,7 +10147,7 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>estado_tachira_8</t>
+          <t>tachira</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Tachira-8.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tachira.xls</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Estado Táchira</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>102</v>
+        <v>1761</v>
       </c>
       <c r="H210" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>4735</v>
+        <v>133843</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
@@ -10194,12 +10194,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>tachira</t>
+          <t>estado_yaracuy_1</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -10214,22 +10214,22 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tachira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy-1.xls</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Yaracuy</t>
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1761</v>
+        <v>57</v>
       </c>
       <c r="H211" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>133843</v>
+        <v>2395</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>estado_yaracuy_1</t>
+          <t>estado_yaracuy</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy.xls</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
@@ -10270,13 +10270,13 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="H212" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>2395</v>
+        <v>807</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>estado_yaracuy</t>
+          <t>estado_yaracuy_4</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Yaracuy-4.xls</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -10317,13 +10317,13 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="H213" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>807</v>
+        <v>2395</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>estado_yaracuy_4</t>
+          <t>yaracuy</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -10355,22 +10355,22 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Yaracuy-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Yaracuy.xls</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>Estado Yaracuy</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>57</v>
+        <v>958</v>
       </c>
       <c r="H214" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>2395</v>
+        <v>72810</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
@@ -10382,12 +10382,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>yaracuy</t>
+          <t>estado_zulia_1</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -10402,22 +10402,22 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Yaracuy.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-1.xls</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Estado Zulia</t>
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>958</v>
+        <v>78</v>
       </c>
       <c r="H215" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>72810</v>
+        <v>3487</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>estado_zulia_1</t>
+          <t>estado_zulia</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia.xls</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
@@ -10461,10 +10461,10 @@
         <v>78</v>
       </c>
       <c r="H216" s="5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>3487</v>
+        <v>807</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>estado_zulia</t>
+          <t>estado_zulia_6</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Zulia-6.xls</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -10508,10 +10508,10 @@
         <v>78</v>
       </c>
       <c r="H217" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>807</v>
+        <v>3487</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>estado_zulia_6</t>
+          <t>zulia</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -10543,22 +10543,22 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Zulia-6.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Zulia.xls</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>Estado Zulia</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>78</v>
+        <v>4825</v>
       </c>
       <c r="H218" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>3487</v>
+        <v>366769</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
@@ -10570,12 +10570,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>zulia</t>
+          <t>coeficiente_gini_2025_1</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Coeficiente GINI</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -10585,27 +10585,27 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Zulia.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Coeficiente-GINI-2025-1.xlsx</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>GINI 2026</t>
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>4825</v>
+        <v>30</v>
       </c>
       <c r="H219" s="5" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>366769</v>
+        <v>57</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
@@ -10617,42 +10617,42 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>edad_simple</t>
+          <t>trabajo_1999_2025_1</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Edad Simple</t>
+          <t>Tabulados Básicos</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/TRABAJO-1999-2025-1.xlsx</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>Edad Simple</t>
+          <t>NACIONAL 1998-2025</t>
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>318</v>
+        <v>523</v>
       </c>
       <c r="H220" s="5" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>3687</v>
+        <v>12018</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
@@ -10664,12 +10664,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>esperanza_de_vida</t>
+          <t>edad_simple</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Esperanza de Vida</t>
+          <t>Edad Simple</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -10684,22 +10684,22 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Esperanza de Vida</t>
+          <t>Edad Simple</t>
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>34</v>
+        <v>318</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>217</v>
+        <v>3687</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
@@ -10711,12 +10711,12 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>nacional_36</t>
+          <t>esperanza_de_vida</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Esperanza de Vida</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -10731,22 +10731,22 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Resumen Entidad</t>
+          <t>Esperanza de Vida</t>
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="H222" s="5" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>4113</v>
+        <v>217</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
@@ -10758,17 +10758,17 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>aragua</t>
+          <t>nacional_36</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -10778,22 +10778,22 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Resumen Entidad</t>
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>671</v>
+        <v>93</v>
       </c>
       <c r="H223" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>50997</v>
+        <v>4113</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>estado_aragua_1</t>
+          <t>aragua</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
@@ -10825,22 +10825,22 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>69</v>
+        <v>671</v>
       </c>
       <c r="H224" s="5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>3019</v>
+        <v>50997</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>estado_aragua</t>
+          <t>estado_aragua_1</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
@@ -10881,13 +10881,13 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H225" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>807</v>
+        <v>3019</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
@@ -10899,49 +10899,96 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
+          <t>estado_aragua</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>Estado Aragua</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>807</v>
+      </c>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K226" s="4" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
           <t>estado_aragua_3</t>
         </is>
       </c>
-      <c r="B226" s="4" t="inlineStr">
+      <c r="B227" s="4" t="inlineStr">
         <is>
           <t>Aragua</t>
         </is>
       </c>
-      <c r="C226" s="4" t="inlineStr">
+      <c r="C227" s="4" t="inlineStr">
         <is>
           <t>Vivienda y servicios</t>
         </is>
       </c>
-      <c r="D226" s="4" t="inlineStr">
-        <is>
-          <t>XLS</t>
-        </is>
-      </c>
-      <c r="E226" s="4" t="inlineStr">
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="F226" s="4" t="inlineStr">
+      <c r="F227" s="4" t="inlineStr">
         <is>
           <t>Estado Aragua</t>
         </is>
       </c>
-      <c r="G226" s="5" t="n">
+      <c r="G227" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="H226" s="5" t="n">
+      <c r="H227" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I226" s="5" t="n">
+      <c r="I227" s="5" t="n">
         <v>3019</v>
       </c>
-      <c r="J226" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K226" s="4" t="inlineStr"/>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K227" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11023,7 +11070,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11117,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14">
@@ -11080,7 +11127,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -11100,7 +11147,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17">
@@ -11110,7 +11157,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2980320</v>
+        <v>2962561</v>
       </c>
     </row>
     <row r="18">

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K227"/>
+  <dimension ref="A1:K229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10570,7 +10570,7 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>coeficiente_gini_2025_1</t>
+          <t>coeficiente_gini</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Coeficiente-GINI-2025-1.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/COEFICIENTE-GINI.xlsx</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>GINI 2026</t>
+          <t>COEFICIENTE GINI</t>
         </is>
       </c>
       <c r="G219" s="5" t="n">
@@ -10617,7 +10617,7 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>trabajo_1999_2025_1</t>
+          <t>trabajo</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -10637,22 +10637,22 @@
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/09/TRABAJO-1999-2025-1.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/TRABAJO.xlsx</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>NACIONAL 1998-2025</t>
+          <t>NACIONAL 1999-2025</t>
         </is>
       </c>
       <c r="G220" s="5" t="n">
         <v>523</v>
       </c>
       <c r="H220" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>12018</v>
+        <v>11611</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
@@ -10664,17 +10664,17 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>edad_simple</t>
+          <t>entidad_federal_y_sexo</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Edad Simple</t>
+          <t>Por Entidad y Sexo</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Población</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -10684,22 +10684,22 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Entidad-Federal-y-Sexo.xls</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Edad Simple</t>
+          <t>Resumen Entidad</t>
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>318</v>
+        <v>86</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>3687</v>
+        <v>4114</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
@@ -10711,12 +10711,12 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>esperanza_de_vida</t>
+          <t>edad_simple</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Esperanza de Vida</t>
+          <t>Edad Simple</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -10731,22 +10731,22 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Esperanza de Vida</t>
+          <t>Edad Simple</t>
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>34</v>
+        <v>318</v>
       </c>
       <c r="H222" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>217</v>
+        <v>3687</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
@@ -10758,12 +10758,12 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>nacional_36</t>
+          <t>esperanza_de_vida</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Esperanza de Vida</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -10778,22 +10778,22 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Resumen Entidad</t>
+          <t>Esperanza de Vida</t>
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="H223" s="5" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>4113</v>
+        <v>217</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
@@ -10805,17 +10805,17 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>aragua</t>
+          <t>nacional_36</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -10825,22 +10825,22 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>n_CEN</t>
+          <t>Resumen Entidad</t>
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>671</v>
+        <v>93</v>
       </c>
       <c r="H224" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>50997</v>
+        <v>4113</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
@@ -10852,17 +10852,17 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>estado_aragua_1</t>
+          <t>proyeccion_poblacion_parroquias</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Por Parroquias</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -10872,22 +10872,22 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/PROYECCION-POBLACION-PARROQUIAS.xls</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>Parroquias</t>
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>69</v>
+        <v>1476</v>
       </c>
       <c r="H225" s="5" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>3019</v>
+        <v>17679</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>estado_aragua</t>
+          <t>aragua</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -10919,22 +10919,22 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>n_CEN</t>
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>78</v>
+        <v>671</v>
       </c>
       <c r="H226" s="5" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>807</v>
+        <v>50997</v>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>estado_aragua_3</t>
+          <t>estado_aragua_1</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -10989,6 +10989,100 @@
         </is>
       </c>
       <c r="K227" s="4" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>estado_aragua</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>Estado Aragua</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I228" s="5" t="n">
+        <v>807</v>
+      </c>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K228" s="4" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>estado_aragua_3</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>Estado Aragua</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="I229" s="5" t="n">
+        <v>3019</v>
+      </c>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K229" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11070,7 +11164,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11211,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14">
@@ -11127,7 +11221,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -11137,7 +11231,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
@@ -11147,7 +11241,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17">
@@ -11157,7 +11251,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2962561</v>
+        <v>2983947</v>
       </c>
     </row>
     <row r="18">

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11164,7 +11164,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11164,7 +11164,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14">
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11164,7 +11164,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11164,7 +11164,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11164,7 +11164,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
